--- a/artfynd/A 34901-2022 artfynd.xlsx
+++ b/artfynd/A 34901-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34901-2022 artfynd.xlsx
+++ b/artfynd/A 34901-2022 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>104316619</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395072.7739881485</v>
+        <v>395073</v>
       </c>
       <c r="R4" t="n">
-        <v>6778407.645040283</v>
+        <v>6778407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1376,7 +1376,7 @@
         <v>104317280</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395112.2768022103</v>
+        <v>395113</v>
       </c>
       <c r="R8" t="n">
-        <v>6778417.104681268</v>
+        <v>6778418</v>
       </c>
       <c r="S8" t="n">
         <v>14</v>
@@ -1845,7 +1845,7 @@
         <v>104739000</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395099.5977992401</v>
+        <v>395099</v>
       </c>
       <c r="R12" t="n">
-        <v>6778414.098024976</v>
+        <v>6778414</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
         <v>104738929</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395016.9238583214</v>
+        <v>395017</v>
       </c>
       <c r="R13" t="n">
-        <v>6778320.83589455</v>
+        <v>6778321</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         <v>104739442</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395430.938962363</v>
+        <v>395431</v>
       </c>
       <c r="R14" t="n">
-        <v>6778435.188394313</v>
+        <v>6778435</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3468,7 +3468,7 @@
         <v>104739446</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395501.8438864886</v>
+        <v>395502</v>
       </c>
       <c r="R26" t="n">
-        <v>6778377.004452842</v>
+        <v>6778377</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 34901-2022 artfynd.xlsx
+++ b/artfynd/A 34901-2022 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>104316619</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>104317280</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>104739000</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>104738929</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>104739442</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>104739446</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 34901-2022 artfynd.xlsx
+++ b/artfynd/A 34901-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103918932</v>
+        <v>104739468</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395441.2773023128</v>
+        <v>395314</v>
       </c>
       <c r="R2" t="n">
-        <v>6778343.025733405</v>
+        <v>6778340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104316792</v>
+        <v>104316805</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394882.960116077</v>
+        <v>394883</v>
       </c>
       <c r="R3" t="n">
-        <v>6778375.110367008</v>
+        <v>6778375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,12 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grov brandhögstubbe.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104316619</v>
+        <v>104739004</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,40 +901,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395073</v>
+        <v>394923</v>
       </c>
       <c r="R4" t="n">
-        <v>6778407</v>
+        <v>6778375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +970,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosöker på insektsangripna granar.</t>
+          <t>På högstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,58 +995,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog, malou lundin</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104316805</v>
+        <v>104739007</v>
       </c>
       <c r="B5" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394882.960116077</v>
+        <v>395075</v>
       </c>
       <c r="R5" t="n">
-        <v>6778375.110367008</v>
+        <v>6778366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,58 +1102,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104316918</v>
+        <v>104738951</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394882.960116077</v>
+        <v>395058</v>
       </c>
       <c r="R6" t="n">
-        <v>6778375.110367008</v>
+        <v>6778355</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På kolade rotben av liggande branstubbe.</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1209,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103919343</v>
+        <v>104738897</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,38 +1227,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>395437.6078741331</v>
+        <v>394887</v>
       </c>
       <c r="R7" t="n">
-        <v>6778415.169138143</v>
+        <v>6778401</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,22 +1281,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt, med apotechier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,59 +1328,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104317280</v>
+        <v>104739345</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fejmån, Dlr</t>
+          <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395113</v>
+        <v>395240</v>
       </c>
       <c r="R8" t="n">
-        <v>6778418</v>
+        <v>6778322</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,27 +1393,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammalt bohål.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,19 +1435,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104738897</v>
+        <v>104739352</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1536,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394886.6554763757</v>
+        <v>395094</v>
       </c>
       <c r="R9" t="n">
-        <v>6778401.590244652</v>
+        <v>6778413</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,27 +1500,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt, med apotechier</t>
+          <t>Ärgnål. Gammal gran. Knappnålslavrik. Ch xyloxena.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104739458</v>
+        <v>104316918</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,37 +1558,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395484.1942180351</v>
+        <v>394883</v>
       </c>
       <c r="R10" t="n">
-        <v>6778418.621255345</v>
+        <v>6778375</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,27 +1613,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt i de flesta träd.</t>
+          <t>På kolade rotben av liggande branstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,37 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104739366</v>
+        <v>104738922</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1770,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>395038.7309863117</v>
+        <v>394894</v>
       </c>
       <c r="R11" t="n">
-        <v>6778386.420215052</v>
+        <v>6778356</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,22 +1725,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På rotben av liggande tidigare  högstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,15 +1772,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104739000</v>
+        <v>104316619</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,9 +1801,10 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1887,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395099</v>
+        <v>395073</v>
       </c>
       <c r="R12" t="n">
-        <v>6778414</v>
+        <v>6778407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1858,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosöker på insektsangripna granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,22 +1883,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Uno Skog, malou lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104738929</v>
+        <v>104317280</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,9 +1919,10 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2004,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395017</v>
+        <v>395113</v>
       </c>
       <c r="R13" t="n">
-        <v>6778321</v>
+        <v>6778418</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +1976,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,15 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104739442</v>
+        <v>104738902</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,14 +2044,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>395431</v>
+        <v>395106</v>
       </c>
       <c r="R14" t="n">
-        <v>6778435</v>
+        <v>6778447</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2151,27 +2078,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringspår på granlåga.</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,15 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104738922</v>
+        <v>104738929</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,34 +2131,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394894.4784008999</v>
+        <v>395017</v>
       </c>
       <c r="R15" t="n">
-        <v>6778355.428317128</v>
+        <v>6778321</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2273,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,12 +2205,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På rotben av liggande tidigare  högstubbe.</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,15 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104739447</v>
+        <v>104738953</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,34 +2243,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>395512.1257737987</v>
+        <v>395096</v>
       </c>
       <c r="R16" t="n">
-        <v>6778348.17567425</v>
+        <v>6778450</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2385,27 +2302,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På uppstående kolat rotben</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,60 +2337,60 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104738905</v>
+        <v>104739000</v>
       </c>
       <c r="B17" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>395092.5515664308</v>
+        <v>395099</v>
       </c>
       <c r="R17" t="n">
-        <v>6778405.122247718</v>
+        <v>6778414</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,7 +2419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,7 +2429,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,57 +2449,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104739456</v>
+        <v>104738905</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>395552.9248191832</v>
+        <v>395093</v>
       </c>
       <c r="R18" t="n">
-        <v>6778368.721370913</v>
+        <v>6778405</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2614,27 +2521,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Allmänt till rikligt med hänglav i hela skogen.</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,50 +2563,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104739459</v>
+        <v>104739366</v>
       </c>
       <c r="B19" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vålbrändan, Dlr</t>
+          <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>395483.1188805472</v>
+        <v>395039</v>
       </c>
       <c r="R19" t="n">
-        <v>6778447.659871239</v>
+        <v>6778386</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2731,27 +2628,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal avverkningsstubbe.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2778,50 +2670,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104738951</v>
+        <v>104316792</v>
       </c>
       <c r="B20" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fejmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>395058.1147942134</v>
+        <v>394883</v>
       </c>
       <c r="R20" t="n">
-        <v>6778354.418016959</v>
+        <v>6778375</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2853,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,7 +2751,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På grov brandhögstubbe.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,22 +2776,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104739345</v>
+        <v>103919343</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,37 +2794,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>395240.667176515</v>
+        <v>395437</v>
       </c>
       <c r="R21" t="n">
-        <v>6778321.91131407</v>
+        <v>6778415</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,22 +2849,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,37 +2891,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104739464</v>
+        <v>104739462</v>
       </c>
       <c r="B22" t="n">
-        <v>76487</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1794</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis haematopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3042,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>395438.8763031787</v>
+        <v>395545</v>
       </c>
       <c r="R22" t="n">
-        <v>6778360.017978271</v>
+        <v>6778371</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3077,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,12 +2971,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Kollekt på gran</t>
+          <t>På lutande senvuxen drygt 200-årig gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,19 +3003,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104739352</v>
+        <v>104739456</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3155,14 +3034,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fejmån, Dlr</t>
+          <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>395094.7168279099</v>
+        <v>395553</v>
       </c>
       <c r="R23" t="n">
-        <v>6778412.793007369</v>
+        <v>6778368</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3189,27 +3068,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ärgnål. Gammal gran. Knappnålslavrik. Ch xyloxena.</t>
+          <t>Allmänt till rikligt med hänglav i hela skogen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,53 +3115,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104739007</v>
+        <v>104739458</v>
       </c>
       <c r="B24" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fejmån, Dlr</t>
+          <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>395075.3927161219</v>
+        <v>395484</v>
       </c>
       <c r="R24" t="n">
-        <v>6778365.506425487</v>
+        <v>6778419</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3306,22 +3180,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i de flesta träd.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,22 +3220,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104739462</v>
+        <v>103918932</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,37 +3238,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>395544.7433883022</v>
+        <v>395441</v>
       </c>
       <c r="R25" t="n">
-        <v>6778370.414290505</v>
+        <v>6778344</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På lutande senvuxen drygt 200-årig gran.</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,15 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104739446</v>
+        <v>104739447</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,39 +3346,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>395502</v>
+        <v>395512</v>
       </c>
       <c r="R26" t="n">
-        <v>6778377</v>
+        <v>6778348</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3545,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3555,7 +3415,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På uppstående kolat rotben</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3582,15 +3447,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104739004</v>
+        <v>104739459</v>
       </c>
       <c r="B27" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,37 +3458,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fejmån, Dlr</t>
+          <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394923.1433275241</v>
+        <v>395483</v>
       </c>
       <c r="R27" t="n">
-        <v>6778374.878582325</v>
+        <v>6778448</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3652,27 +3512,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På högstubbe.</t>
+          <t>På gammal avverkningsstubbe.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,61 +3552,60 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103919865</v>
+        <v>104739442</v>
       </c>
       <c r="B28" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>395416.9624009761</v>
+        <v>395431</v>
       </c>
       <c r="R28" t="n">
-        <v>6778355.833861529</v>
+        <v>6778435</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3775,7 +3634,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3785,12 +3644,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På björkstubbe.</t>
+          <t>Gamla ringspår på granlåga.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3817,54 +3676,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103918927</v>
+        <v>104739446</v>
       </c>
       <c r="B29" t="n">
-        <v>76487</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1794</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis haematopus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vålbrändan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>395441.2773023128</v>
+        <v>395502</v>
       </c>
       <c r="R29" t="n">
-        <v>6778343.025733405</v>
+        <v>6778377</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,7 +3751,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3903,14 +3761,14 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3927,6 +3785,227 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>103919865</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vålbrändan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>395417</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6778356</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På björkstubbe.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103917862</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vålbrändan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>395533</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6778359</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34901-2022 artfynd.xlsx
+++ b/artfynd/A 34901-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103919343</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738951</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738897</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739345</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739352</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739456</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739458</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103918932</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316918</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738922</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739447</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739459</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316619</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104317280</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2893,6 +2993,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738902</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738929</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3117,6 +3227,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738953</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3229,6 +3344,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739000</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739442</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3458,6 +3583,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739446</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3565,6 +3695,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104738905</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3672,6 +3807,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739366</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3785,6 +3925,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103919865</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3898,6 +4043,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316792</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4006,8 +4156,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103917862</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>